--- a/data/trans_orig/P15-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P15-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2007</t>
+          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12019</t>
+          <t>12122</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27717</t>
+          <t>28520</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8336</t>
+          <t>8660</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24646</t>
+          <t>24434</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23676</t>
+          <t>23156</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46501</t>
+          <t>46358</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,68%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>245293</t>
+          <t>244490</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>260991</t>
+          <t>260888</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>236192</t>
+          <t>236404</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>252502</t>
+          <t>252178</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>487347</t>
+          <t>487490</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>510172</t>
+          <t>510692</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,66%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12553</t>
+          <t>11808</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33170</t>
+          <t>30889</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11008</t>
+          <t>11224</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27814</t>
+          <t>29572</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27825</t>
+          <t>26581</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54172</t>
+          <t>51893</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>459905</t>
+          <t>462186</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>480522</t>
+          <t>481267</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>476135</t>
+          <t>474377</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>492941</t>
+          <t>492725</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>942852</t>
+          <t>945131</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>969199</t>
+          <t>970443</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,33%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22011</t>
+          <t>22272</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43919</t>
+          <t>43138</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9055</t>
+          <t>8656</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25955</t>
+          <t>25058</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35278</t>
+          <t>34569</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62083</t>
+          <t>61004</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,32%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>274927</t>
+          <t>275708</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>296835</t>
+          <t>296574</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>309457</t>
+          <t>310354</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>326357</t>
+          <t>326756</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>592175</t>
+          <t>593254</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>618980</t>
+          <t>619689</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,72%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28581</t>
+          <t>29565</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52032</t>
+          <t>52924</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13250</t>
+          <t>13088</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30814</t>
+          <t>31288</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46079</t>
+          <t>48751</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>76929</t>
+          <t>80694</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>306639</t>
+          <t>305747</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>330090</t>
+          <t>329106</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>340642</t>
+          <t>340168</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>358206</t>
+          <t>358368</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>653198</t>
+          <t>649433</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>684048</t>
+          <t>681376</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,32%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12349</t>
+          <t>11632</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29294</t>
+          <t>30677</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6944</t>
+          <t>7023</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21574</t>
+          <t>21376</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22582</t>
+          <t>23100</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44813</t>
+          <t>46036</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,2%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>174014</t>
+          <t>172631</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>190959</t>
+          <t>191676</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>186094</t>
+          <t>186292</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>200724</t>
+          <t>200645</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>366163</t>
+          <t>364940</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>388394</t>
+          <t>387876</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,38%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11702</t>
+          <t>12092</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29460</t>
+          <t>29633</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13419</t>
+          <t>13388</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>32011</t>
+          <t>31190</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>31094</t>
+          <t>30478</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>55957</t>
+          <t>56211</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,24%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>241351</t>
+          <t>241178</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>259109</t>
+          <t>258719</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>246133</t>
+          <t>246954</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>264725</t>
+          <t>264756</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>492998</t>
+          <t>492744</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>517861</t>
+          <t>518477</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,45%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>33345</t>
+          <t>33839</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>61186</t>
+          <t>61208</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15792</t>
+          <t>15436</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>36233</t>
+          <t>33896</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>54167</t>
+          <t>54541</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>86684</t>
+          <t>88107</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>553841</t>
+          <t>553819</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>581682</t>
+          <t>581188</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>601986</t>
+          <t>604323</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>622427</t>
+          <t>622783</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1166562</t>
+          <t>1165139</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1199079</t>
+          <t>1198705</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,65%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>36840</t>
+          <t>36311</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>65832</t>
+          <t>63259</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>36405</t>
+          <t>35674</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>63651</t>
+          <t>62623</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>77936</t>
+          <t>79669</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>115686</t>
+          <t>117879</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>677963</t>
+          <t>680536</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>706955</t>
+          <t>707484</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>719860</t>
+          <t>720888</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>747106</t>
+          <t>747837</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1411620</t>
+          <t>1409427</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1449370</t>
+          <t>1447637</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,78%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>213412</t>
+          <t>212290</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>272920</t>
+          <t>275280</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>151081</t>
+          <t>151993</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>206321</t>
+          <t>204526</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>379017</t>
+          <t>381713</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>461354</t>
+          <t>466311</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3003623</t>
+          <t>3001263</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3063131</t>
+          <t>3064253</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3172876</t>
+          <t>3174671</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3228116</t>
+          <t>3227204</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6194387</t>
+          <t>6189430</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6276724</t>
+          <t>6274028</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,26%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2012</t>
+          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25706</t>
+          <t>26142</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48917</t>
+          <t>49492</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18470</t>
+          <t>17545</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40046</t>
+          <t>39323</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50430</t>
+          <t>49116</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>83036</t>
+          <t>81308</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>13,97%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>245821</t>
+          <t>245246</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>269032</t>
+          <t>268596</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>247199</t>
+          <t>247922</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>268775</t>
+          <t>269700</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>498947</t>
+          <t>500675</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>531553</t>
+          <t>532867</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,56%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22545</t>
+          <t>22862</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45373</t>
+          <t>45243</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20837</t>
+          <t>20951</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42667</t>
+          <t>42477</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48077</t>
+          <t>47157</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>81272</t>
+          <t>78566</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>460154</t>
+          <t>460284</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>482982</t>
+          <t>482665</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>481098</t>
+          <t>481288</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>502928</t>
+          <t>502814</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>948020</t>
+          <t>950726</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>981215</t>
+          <t>982135</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,42%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41356</t>
+          <t>40644</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>66452</t>
+          <t>67457</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30044</t>
+          <t>29356</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55310</t>
+          <t>53691</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>77572</t>
+          <t>77816</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>112011</t>
+          <t>113934</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,13%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>257594</t>
+          <t>256589</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>282690</t>
+          <t>283402</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>285710</t>
+          <t>287329</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>310976</t>
+          <t>311664</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>553055</t>
+          <t>551132</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>587494</t>
+          <t>587250</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,3%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21951</t>
+          <t>22684</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46210</t>
+          <t>46231</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10725</t>
+          <t>11062</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26822</t>
+          <t>26997</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35176</t>
+          <t>37191</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>65374</t>
+          <t>66995</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>327772</t>
+          <t>327751</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>352031</t>
+          <t>351298</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>362129</t>
+          <t>361954</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>378226</t>
+          <t>377889</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>697559</t>
+          <t>695938</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>727757</t>
+          <t>725742</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,13%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>7341</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21662</t>
+          <t>22134</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12231</t>
+          <t>12070</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29820</t>
+          <t>30591</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24674</t>
+          <t>23340</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>46047</t>
+          <t>44868</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>190956</t>
+          <t>190484</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>205537</t>
+          <t>205277</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>189771</t>
+          <t>189000</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>207360</t>
+          <t>207521</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>386162</t>
+          <t>387341</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>407535</t>
+          <t>408869</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,6%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21540</t>
+          <t>20797</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>42948</t>
+          <t>42858</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26767</t>
+          <t>24636</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>47781</t>
+          <t>47689</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>51901</t>
+          <t>51342</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>83055</t>
+          <t>82003</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,8%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>231033</t>
+          <t>231123</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>252441</t>
+          <t>253184</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>232250</t>
+          <t>232342</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>253264</t>
+          <t>255395</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>470957</t>
+          <t>472009</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>502111</t>
+          <t>502670</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,73%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>51871</t>
+          <t>51855</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>82609</t>
+          <t>82788</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>46890</t>
+          <t>45585</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>75912</t>
+          <t>75268</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>106416</t>
+          <t>106490</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>149941</t>
+          <t>147921</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,9%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>580179</t>
+          <t>580000</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>610917</t>
+          <t>610933</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>617941</t>
+          <t>618585</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>646963</t>
+          <t>648268</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1206700</t>
+          <t>1208720</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1250225</t>
+          <t>1250151</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,15%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14882</t>
+          <t>15629</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>36256</t>
+          <t>36628</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>17141</t>
+          <t>17729</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>38780</t>
+          <t>38573</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>36577</t>
+          <t>37326</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>66079</t>
+          <t>69570</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>742842</t>
+          <t>742470</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>764216</t>
+          <t>763469</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>785073</t>
+          <t>785280</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>806712</t>
+          <t>806124</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1536872</t>
+          <t>1533381</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1566374</t>
+          <t>1565625</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,67%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>254257</t>
+          <t>255444</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>323070</t>
+          <t>320308</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>226504</t>
+          <t>230061</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>290278</t>
+          <t>294681</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>498305</t>
+          <t>494687</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>592513</t>
+          <t>591726</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3103709</t>
+          <t>3106471</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3172522</t>
+          <t>3171335</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3268031</t>
+          <t>3263628</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3331805</t>
+          <t>3328248</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6392575</t>
+          <t>6393362</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6486783</t>
+          <t>6490401</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,92%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2016</t>
+          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11689</t>
+          <t>12038</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29326</t>
+          <t>30533</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21097</t>
+          <t>21190</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42654</t>
+          <t>45026</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37280</t>
+          <t>36488</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>65996</t>
+          <t>63547</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>10,91%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>264435</t>
+          <t>263228</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>282072</t>
+          <t>281723</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>246049</t>
+          <t>243677</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>267606</t>
+          <t>267513</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>516468</t>
+          <t>518917</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>545184</t>
+          <t>545976</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,74%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11260</t>
+          <t>11580</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29066</t>
+          <t>30468</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9122</t>
+          <t>9379</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25182</t>
+          <t>25795</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23975</t>
+          <t>25137</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>49436</t>
+          <t>48707</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>473509</t>
+          <t>472107</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>491315</t>
+          <t>490995</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>497902</t>
+          <t>497289</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>513962</t>
+          <t>513705</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>976223</t>
+          <t>976952</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1001684</t>
+          <t>1000522</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,55%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15562</t>
+          <t>15445</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34703</t>
+          <t>33915</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7335</t>
+          <t>7589</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21949</t>
+          <t>22368</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26397</t>
+          <t>26021</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50471</t>
+          <t>49355</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>283862</t>
+          <t>284650</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>303003</t>
+          <t>303120</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>314360</t>
+          <t>313941</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>328974</t>
+          <t>328720</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>604403</t>
+          <t>605519</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>628477</t>
+          <t>628853</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,03%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26638</t>
+          <t>26204</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52060</t>
+          <t>51463</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25139</t>
+          <t>25838</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49946</t>
+          <t>49289</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>59688</t>
+          <t>59318</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>93974</t>
+          <t>94683</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,5%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>317904</t>
+          <t>318501</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>343326</t>
+          <t>343760</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>337337</t>
+          <t>337994</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>362144</t>
+          <t>361445</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>663273</t>
+          <t>662564</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>697559</t>
+          <t>697929</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,17%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>5497</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16930</t>
+          <t>17722</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>1181</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10366</t>
+          <t>11289</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8658</t>
+          <t>8324</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23941</t>
+          <t>23297</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>194291</t>
+          <t>193499</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>205730</t>
+          <t>205724</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>208221</t>
+          <t>207298</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>217469</t>
+          <t>217406</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>405867</t>
+          <t>406511</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>421150</t>
+          <t>421484</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,06%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19630</t>
+          <t>19277</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>39925</t>
+          <t>38380</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26121</t>
+          <t>26536</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>49609</t>
+          <t>48258</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>51142</t>
+          <t>50619</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>81735</t>
+          <t>81994</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,29%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>223198</t>
+          <t>224743</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>243493</t>
+          <t>243846</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>223506</t>
+          <t>224857</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>246994</t>
+          <t>246579</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>454503</t>
+          <t>454244</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>485096</t>
+          <t>485619</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,56%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17787</t>
+          <t>17414</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39137</t>
+          <t>38555</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17903</t>
+          <t>17679</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>39211</t>
+          <t>40566</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>41044</t>
+          <t>39980</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>70661</t>
+          <t>70046</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>617421</t>
+          <t>618003</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>638771</t>
+          <t>639144</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>652083</t>
+          <t>650728</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>673391</t>
+          <t>673615</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1277191</t>
+          <t>1277806</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1306808</t>
+          <t>1307872</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>97,03%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>24377</t>
+          <t>24536</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>47205</t>
+          <t>48204</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>17608</t>
+          <t>17717</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>39328</t>
+          <t>38422</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>47824</t>
+          <t>47180</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>79336</t>
+          <t>79161</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>731378</t>
+          <t>730379</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>754206</t>
+          <t>754047</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>786839</t>
+          <t>787745</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>808559</t>
+          <t>808450</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1525414</t>
+          <t>1525589</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1556926</t>
+          <t>1557570</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,06%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>172348</t>
+          <t>174325</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>227456</t>
+          <t>228532</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>166967</t>
+          <t>163810</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>219653</t>
+          <t>219660</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>354579</t>
+          <t>355480</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>431587</t>
+          <t>430098</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3166894</t>
+          <t>3165818</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3222002</t>
+          <t>3220025</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3324889</t>
+          <t>3324882</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3377575</t>
+          <t>3380732</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6507305</t>
+          <t>6508794</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6584313</t>
+          <t>6583412</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,88%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2023</t>
+          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18039</t>
+          <t>18361</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44618</t>
+          <t>44750</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22189</t>
+          <t>22542</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36983</t>
+          <t>37127</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45678</t>
+          <t>45387</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>74381</t>
+          <t>75641</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>266825</t>
+          <t>266693</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>293404</t>
+          <t>293082</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>252652</t>
+          <t>252508</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>267446</t>
+          <t>267093</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>526696</t>
+          <t>525436</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>555399</t>
+          <t>555690</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,45%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14655</t>
+          <t>14888</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38177</t>
+          <t>38313</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24669</t>
+          <t>25273</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44704</t>
+          <t>44809</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44004</t>
+          <t>44744</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>75172</t>
+          <t>75178</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>480213</t>
+          <t>480077</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>503735</t>
+          <t>503502</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>470265</t>
+          <t>470160</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>490300</t>
+          <t>489696</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>958187</t>
+          <t>958181</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>989355</t>
+          <t>988615</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,67%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14203</t>
+          <t>14693</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30764</t>
+          <t>32277</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19707</t>
+          <t>19560</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36225</t>
+          <t>36160</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37869</t>
+          <t>37916</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>60443</t>
+          <t>61616</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>285286</t>
+          <t>283773</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>301847</t>
+          <t>301357</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>312903</t>
+          <t>312968</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>329421</t>
+          <t>329568</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>604735</t>
+          <t>603562</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>627309</t>
+          <t>627262</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,3%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13869</t>
+          <t>12923</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39220</t>
+          <t>37813</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9207</t>
+          <t>9790</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31542</t>
+          <t>32658</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26734</t>
+          <t>24992</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>62230</t>
+          <t>62967</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,99%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>273337</t>
+          <t>274744</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>298688</t>
+          <t>299634</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>444176</t>
+          <t>443060</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>466511</t>
+          <t>465928</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>726044</t>
+          <t>725307</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>761540</t>
+          <t>763282</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,83%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3391</t>
+          <t>3408</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14839</t>
+          <t>14032</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2969</t>
+          <t>3262</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>3673</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14609</t>
+          <t>15118</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>163903</t>
+          <t>164710</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>175351</t>
+          <t>175334</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,7 +12222,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>205687</t>
+          <t>205394</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>372789</t>
+          <t>372280</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>383618</t>
+          <t>383725</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18755</t>
+          <t>18708</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36162</t>
+          <t>36212</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20556</t>
+          <t>20450</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34762</t>
+          <t>35123</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>43352</t>
+          <t>43280</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>67049</t>
+          <t>64972</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,34%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>233474</t>
+          <t>233424</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>250881</t>
+          <t>250928</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>222294</t>
+          <t>221933</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>236500</t>
+          <t>236606</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>459643</t>
+          <t>461720</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>483340</t>
+          <t>483412</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,78%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31085</t>
+          <t>30970</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>59177</t>
+          <t>59570</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>25607</t>
+          <t>21447</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>72190</t>
+          <t>73560</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>56076</t>
+          <t>56359</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>118634</t>
+          <t>119374</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,1%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>565102</t>
+          <t>564709</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>593194</t>
+          <t>593309</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>777075</t>
+          <t>775705</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>823658</t>
+          <t>827818</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1354910</t>
+          <t>1354170</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1417468</t>
+          <t>1417185</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,18%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9780</t>
+          <t>10361</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>41033</t>
+          <t>41222</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>20986</t>
+          <t>21205</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>38853</t>
+          <t>39507</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>31824</t>
+          <t>32849</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>73064</t>
+          <t>72603</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>887687</t>
+          <t>887498</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>918940</t>
+          <t>918359</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>678878</t>
+          <t>678224</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>696745</t>
+          <t>696526</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1573388</t>
+          <t>1573849</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1614628</t>
+          <t>1613603</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,0%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>156189</t>
+          <t>153650</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>237795</t>
+          <t>236555</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>177727</t>
+          <t>172841</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>248580</t>
+          <t>242043</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>354667</t>
+          <t>352614</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>462516</t>
+          <t>461129</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3222022</t>
+          <t>3223262</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3303628</t>
+          <t>3306167</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3413577</t>
+          <t>3420114</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3484430</t>
+          <t>3489316</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6659458</t>
+          <t>6660845</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6767307</t>
+          <t>6769360</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,05%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P15-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P15-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12122</t>
+          <t>11857</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28520</t>
+          <t>28389</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8660</t>
+          <t>7820</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24434</t>
+          <t>25260</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23156</t>
+          <t>23788</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46358</t>
+          <t>46749</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>244490</t>
+          <t>244621</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>260888</t>
+          <t>261153</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>236404</t>
+          <t>235578</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>252178</t>
+          <t>253018</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>487490</t>
+          <t>487099</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>510692</t>
+          <t>510060</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,54%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11808</t>
+          <t>12528</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30889</t>
+          <t>31484</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11224</t>
+          <t>11115</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29572</t>
+          <t>28132</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26581</t>
+          <t>27450</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51893</t>
+          <t>52704</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>462186</t>
+          <t>461591</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>481267</t>
+          <t>480547</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>474377</t>
+          <t>475817</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>492725</t>
+          <t>492834</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>945131</t>
+          <t>944320</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>970443</t>
+          <t>969574</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,25%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22272</t>
+          <t>22042</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43138</t>
+          <t>44272</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8656</t>
+          <t>9279</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25058</t>
+          <t>25465</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34569</t>
+          <t>35133</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61004</t>
+          <t>63425</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,69%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>275708</t>
+          <t>274574</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>296574</t>
+          <t>296804</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>310354</t>
+          <t>309947</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>326756</t>
+          <t>326133</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>593254</t>
+          <t>590833</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>619689</t>
+          <t>619125</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,63%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29565</t>
+          <t>29910</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52924</t>
+          <t>51586</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13088</t>
+          <t>12855</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31288</t>
+          <t>30492</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>48751</t>
+          <t>47683</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>80694</t>
+          <t>75904</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,4%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>305747</t>
+          <t>307085</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>329106</t>
+          <t>328761</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>340168</t>
+          <t>340964</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>358368</t>
+          <t>358601</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>649433</t>
+          <t>654223</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>681376</t>
+          <t>682444</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,47%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11632</t>
+          <t>12571</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30677</t>
+          <t>29208</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7023</t>
+          <t>6716</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21376</t>
+          <t>22358</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23100</t>
+          <t>21942</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>46036</t>
+          <t>44802</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>10,9%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>172631</t>
+          <t>174100</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>191676</t>
+          <t>190737</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>186292</t>
+          <t>185310</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>200645</t>
+          <t>200952</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>364940</t>
+          <t>366174</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>387876</t>
+          <t>389034</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,66%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12092</t>
+          <t>12082</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29633</t>
+          <t>29612</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13388</t>
+          <t>13562</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31190</t>
+          <t>32297</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>30478</t>
+          <t>29676</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>56211</t>
+          <t>54160</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>9,87%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>241178</t>
+          <t>241199</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>258719</t>
+          <t>258729</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>246954</t>
+          <t>245847</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>264756</t>
+          <t>264582</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>492744</t>
+          <t>494795</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>518477</t>
+          <t>519279</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,59%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>33839</t>
+          <t>32335</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>61208</t>
+          <t>60765</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15436</t>
+          <t>15506</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>33896</t>
+          <t>35278</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>54541</t>
+          <t>53279</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>88107</t>
+          <t>85764</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,84%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>553819</t>
+          <t>554262</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>581188</t>
+          <t>582692</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>604323</t>
+          <t>602941</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>622783</t>
+          <t>622713</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1165139</t>
+          <t>1167482</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1198705</t>
+          <t>1199967</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,75%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>36311</t>
+          <t>35884</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>63259</t>
+          <t>62428</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>35674</t>
+          <t>35124</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>62623</t>
+          <t>62378</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>79669</t>
+          <t>79312</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>117879</t>
+          <t>118717</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>680536</t>
+          <t>681367</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>707484</t>
+          <t>707911</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>720888</t>
+          <t>721133</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>747837</t>
+          <t>748387</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1409427</t>
+          <t>1408589</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1447637</t>
+          <t>1447994</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,81%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>212290</t>
+          <t>215378</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>275280</t>
+          <t>275818</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>151993</t>
+          <t>151737</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>204526</t>
+          <t>203313</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>381713</t>
+          <t>376930</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>466311</t>
+          <t>462125</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3001263</t>
+          <t>3000725</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3064253</t>
+          <t>3061165</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3174671</t>
+          <t>3175884</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3227204</t>
+          <t>3227460</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6189430</t>
+          <t>6193616</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6274028</t>
+          <t>6278811</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,34%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26142</t>
+          <t>27145</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49492</t>
+          <t>50399</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17545</t>
+          <t>18217</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39323</t>
+          <t>39261</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49116</t>
+          <t>50190</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81308</t>
+          <t>82310</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,14%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>245246</t>
+          <t>244339</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>268596</t>
+          <t>267593</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>247922</t>
+          <t>247984</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>269700</t>
+          <t>269028</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>500675</t>
+          <t>499673</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>532867</t>
+          <t>531793</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,38%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22862</t>
+          <t>22943</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45243</t>
+          <t>44323</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20951</t>
+          <t>21267</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42477</t>
+          <t>43363</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>47157</t>
+          <t>48085</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>78566</t>
+          <t>78547</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>460284</t>
+          <t>461204</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>482665</t>
+          <t>482584</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>481288</t>
+          <t>480402</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>502814</t>
+          <t>502498</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>950726</t>
+          <t>950745</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>982135</t>
+          <t>981207</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,33%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40644</t>
+          <t>41617</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>67457</t>
+          <t>65758</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29356</t>
+          <t>30421</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53691</t>
+          <t>54931</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>77816</t>
+          <t>78420</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>113934</t>
+          <t>115305</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,34%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>256589</t>
+          <t>258288</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>283402</t>
+          <t>282429</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>287329</t>
+          <t>286089</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>311664</t>
+          <t>310599</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>551132</t>
+          <t>549761</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>587250</t>
+          <t>586646</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,21%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22684</t>
+          <t>22769</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46231</t>
+          <t>46769</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11062</t>
+          <t>10620</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26997</t>
+          <t>28417</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37191</t>
+          <t>36177</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66995</t>
+          <t>66696</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>327751</t>
+          <t>327213</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>351298</t>
+          <t>351213</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>361954</t>
+          <t>360534</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>377889</t>
+          <t>378331</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>695938</t>
+          <t>696237</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>725742</t>
+          <t>726756</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,26%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7341</t>
+          <t>7286</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22134</t>
+          <t>21193</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12070</t>
+          <t>12204</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30591</t>
+          <t>29568</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23340</t>
+          <t>23736</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44868</t>
+          <t>45426</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,51%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>190484</t>
+          <t>191425</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>205277</t>
+          <t>205332</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>189000</t>
+          <t>190023</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>207521</t>
+          <t>207387</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>387341</t>
+          <t>386783</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>408869</t>
+          <t>408473</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,51%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20797</t>
+          <t>21218</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>42858</t>
+          <t>42909</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24636</t>
+          <t>24801</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>47689</t>
+          <t>48406</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>51342</t>
+          <t>50631</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>82003</t>
+          <t>83151</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>15,01%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>231123</t>
+          <t>231072</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>253184</t>
+          <t>252763</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>232342</t>
+          <t>231625</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>255395</t>
+          <t>255230</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>472009</t>
+          <t>470861</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>502670</t>
+          <t>503381</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,86%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>51855</t>
+          <t>51676</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>82788</t>
+          <t>85276</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>45585</t>
+          <t>45795</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>75268</t>
+          <t>75477</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>106490</t>
+          <t>106183</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>147921</t>
+          <t>147415</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>580000</t>
+          <t>577512</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>610933</t>
+          <t>611112</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>618585</t>
+          <t>618376</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>648268</t>
+          <t>648058</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1208720</t>
+          <t>1209226</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1250151</t>
+          <t>1250458</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,17%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>15629</t>
+          <t>15707</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>36628</t>
+          <t>36055</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,47 +6472,47 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>4,63%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>26357</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>16579</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>37600</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
           <t>2,01%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>4,7%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>26357</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>17729</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>38573</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>3,2%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>37326</t>
+          <t>37416</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>69570</t>
+          <t>66697</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>742470</t>
+          <t>743043</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>763469</t>
+          <t>763391</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,49 +6585,49 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
+          <t>97,98%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>734</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>797496</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>786253</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>807274</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>96,8%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>95,44%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
           <t>97,99%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>734</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>797496</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>785280</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>806124</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>96,8%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>95,32%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>97,85%</t>
-        </is>
-      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>1429</t>
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1533381</t>
+          <t>1536254</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1565625</t>
+          <t>1565535</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>255444</t>
+          <t>253974</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>320308</t>
+          <t>325624</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>230061</t>
+          <t>225598</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>294681</t>
+          <t>290532</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>494687</t>
+          <t>499453</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>591726</t>
+          <t>596415</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3106471</t>
+          <t>3101155</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3171335</t>
+          <t>3172805</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3263628</t>
+          <t>3267777</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3328248</t>
+          <t>3332711</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6393362</t>
+          <t>6388673</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6490401</t>
+          <t>6485635</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,85%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12038</t>
+          <t>12676</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30533</t>
+          <t>29300</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21190</t>
+          <t>19446</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45026</t>
+          <t>41026</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36488</t>
+          <t>37661</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63547</t>
+          <t>65871</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,31%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>263228</t>
+          <t>264461</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>281723</t>
+          <t>281085</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>243677</t>
+          <t>247677</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>267513</t>
+          <t>269257</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>518917</t>
+          <t>516593</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>545976</t>
+          <t>544803</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,53%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11580</t>
+          <t>12196</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30468</t>
+          <t>29519</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9379</t>
+          <t>8589</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25795</t>
+          <t>26494</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25137</t>
+          <t>24370</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>48707</t>
+          <t>48284</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>472107</t>
+          <t>473056</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>490995</t>
+          <t>490379</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>497289</t>
+          <t>496590</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>513705</t>
+          <t>514495</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>976952</t>
+          <t>977375</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1000522</t>
+          <t>1001289</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,62%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15445</t>
+          <t>15101</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33915</t>
+          <t>32999</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7589</t>
+          <t>7507</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22368</t>
+          <t>22690</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26021</t>
+          <t>26622</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>49355</t>
+          <t>49741</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>284650</t>
+          <t>285566</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>303120</t>
+          <t>303464</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>313941</t>
+          <t>313619</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>328720</t>
+          <t>328802</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>605519</t>
+          <t>605133</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>628853</t>
+          <t>628252</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,93%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26204</t>
+          <t>27625</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51463</t>
+          <t>53497</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25838</t>
+          <t>24908</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49289</t>
+          <t>51857</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>59318</t>
+          <t>58182</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>94683</t>
+          <t>93362</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,33%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>318501</t>
+          <t>316467</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>343760</t>
+          <t>342339</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>337994</t>
+          <t>335426</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>361445</t>
+          <t>362375</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>662564</t>
+          <t>663885</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>697929</t>
+          <t>699065</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,32%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5497</t>
+          <t>5484</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17722</t>
+          <t>17372</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1181</t>
+          <t>1123</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11289</t>
+          <t>11473</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8324</t>
+          <t>8737</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23297</t>
+          <t>24231</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>193499</t>
+          <t>193849</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>205724</t>
+          <t>205737</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>207298</t>
+          <t>207114</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>217406</t>
+          <t>217464</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>406511</t>
+          <t>405577</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>421484</t>
+          <t>421071</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>97,97%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19277</t>
+          <t>18588</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>38380</t>
+          <t>38382</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,7 +9109,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26536</t>
+          <t>24851</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>48258</t>
+          <t>48219</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>50619</t>
+          <t>51859</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>81994</t>
+          <t>81724</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,24%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>224743</t>
+          <t>224741</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>243846</t>
+          <t>244535</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9227,7 +9227,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>224857</t>
+          <t>224896</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>246579</t>
+          <t>248264</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>454244</t>
+          <t>454514</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>485619</t>
+          <t>484379</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,33%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17414</t>
+          <t>17302</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38555</t>
+          <t>37994</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17679</t>
+          <t>18197</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>40566</t>
+          <t>39570</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>39980</t>
+          <t>41099</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>70046</t>
+          <t>69685</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>618003</t>
+          <t>618564</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>639144</t>
+          <t>639256</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>650728</t>
+          <t>651724</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>673615</t>
+          <t>673097</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1277806</t>
+          <t>1278167</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1307872</t>
+          <t>1306753</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,95%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>24536</t>
+          <t>24243</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>48204</t>
+          <t>48440</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>17717</t>
+          <t>18023</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>38422</t>
+          <t>38217</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>47180</t>
+          <t>47340</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>79161</t>
+          <t>77379</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>730379</t>
+          <t>730143</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>754047</t>
+          <t>754340</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>787745</t>
+          <t>787950</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>808450</t>
+          <t>808144</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1525589</t>
+          <t>1527371</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1557570</t>
+          <t>1557410</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,05%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>174325</t>
+          <t>171341</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>228532</t>
+          <t>229041</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>163810</t>
+          <t>165479</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>219660</t>
+          <t>222649</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>355480</t>
+          <t>353845</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>430098</t>
+          <t>430711</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3165818</t>
+          <t>3165309</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3220025</t>
+          <t>3223009</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3324882</t>
+          <t>3321893</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3380732</t>
+          <t>3379063</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6508794</t>
+          <t>6508181</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6583412</t>
+          <t>6585047</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,9%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>28092</t>
+          <t>27039</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18361</t>
+          <t>18227</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44750</t>
+          <t>39122</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>28977</t>
+          <t>30435</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22542</t>
+          <t>23328</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37127</t>
+          <t>38887</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>57069</t>
+          <t>57474</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45387</t>
+          <t>46253</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75641</t>
+          <t>72753</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>11,46%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>283351</t>
+          <t>291806</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>266693</t>
+          <t>279723</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>293082</t>
+          <t>300618</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>260658</t>
+          <t>285626</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>252508</t>
+          <t>277174</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>267093</t>
+          <t>292733</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>544008</t>
+          <t>577432</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>525436</t>
+          <t>562153</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>555690</t>
+          <t>588653</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,71%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24343</t>
+          <t>24703</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14888</t>
+          <t>15180</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38313</t>
+          <t>38879</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>33363</t>
+          <t>34730</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25273</t>
+          <t>24437</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44809</t>
+          <t>44941</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>57705</t>
+          <t>59433</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44744</t>
+          <t>46281</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>75178</t>
+          <t>76230</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>494047</t>
+          <t>505944</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>480077</t>
+          <t>491768</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>503502</t>
+          <t>515467</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>481606</t>
+          <t>511764</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>470160</t>
+          <t>501553</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>489696</t>
+          <t>522057</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>975654</t>
+          <t>1017708</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>958181</t>
+          <t>1000911</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>988615</t>
+          <t>1030860</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,7%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>21332</t>
+          <t>22311</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14693</t>
+          <t>15163</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32277</t>
+          <t>31800</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>26796</t>
+          <t>26705</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19560</t>
+          <t>19698</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36160</t>
+          <t>36626</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>48128</t>
+          <t>49015</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37916</t>
+          <t>39915</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61616</t>
+          <t>61171</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>294718</t>
+          <t>293682</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>283773</t>
+          <t>284193</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>301357</t>
+          <t>300830</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>322332</t>
+          <t>329676</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>312968</t>
+          <t>319755</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>329568</t>
+          <t>336683</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>617050</t>
+          <t>623360</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>603562</t>
+          <t>611204</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>627262</t>
+          <t>632460</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,06%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>23751</t>
+          <t>28096</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12923</t>
+          <t>15958</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37813</t>
+          <t>47152</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>18212</t>
+          <t>19399</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9790</t>
+          <t>11716</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32658</t>
+          <t>34189</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>41964</t>
+          <t>47494</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24992</t>
+          <t>32123</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>62967</t>
+          <t>68806</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,65%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>288806</t>
+          <t>345049</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>274744</t>
+          <t>325993</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>299634</t>
+          <t>357187</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>457506</t>
+          <t>402562</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>443060</t>
+          <t>387772</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>465928</t>
+          <t>410245</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>746310</t>
+          <t>747613</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>725307</t>
+          <t>726301</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>763282</t>
+          <t>762984</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>95,96%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7491</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3408</t>
+          <t>3629</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14032</t>
+          <t>15017</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,7 +12104,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>525</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -12114,12 +12114,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3262</t>
+          <t>2897</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>7653</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3673</t>
+          <t>3715</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15118</t>
+          <t>15210</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>171629</t>
+          <t>198174</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>164710</t>
+          <t>190648</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>175334</t>
+          <t>202036</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,27 +12217,27 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>208116</t>
+          <t>226690</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>205394</t>
+          <t>224318</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>379745</t>
+          <t>424863</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>372280</t>
+          <t>417669</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>383725</t>
+          <t>429164</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>26033</t>
+          <t>26018</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18708</t>
+          <t>19314</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36212</t>
+          <t>35250</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>26997</t>
+          <t>28130</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20450</t>
+          <t>21857</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35123</t>
+          <t>36111</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>53030</t>
+          <t>54148</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>43280</t>
+          <t>43246</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>64972</t>
+          <t>65184</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,2%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>243603</t>
+          <t>244689</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>233424</t>
+          <t>235457</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>250928</t>
+          <t>251393</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>230059</t>
+          <t>235620</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>221933</t>
+          <t>227639</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>236606</t>
+          <t>241893</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>473662</t>
+          <t>480309</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>461720</t>
+          <t>469273</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>483412</t>
+          <t>491211</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,91%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>43439</t>
+          <t>55803</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30970</t>
+          <t>41689</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>59570</t>
+          <t>75307</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>50106</t>
+          <t>58433</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21447</t>
+          <t>46595</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>73560</t>
+          <t>73082</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>93546</t>
+          <t>114236</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>56359</t>
+          <t>94384</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>119374</t>
+          <t>140038</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>9,39%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>580840</t>
+          <t>663884</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>564709</t>
+          <t>644380</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>593309</t>
+          <t>677998</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>799159</t>
+          <t>713624</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>775705</t>
+          <t>698975</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>827818</t>
+          <t>725462</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1379998</t>
+          <t>1377508</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1354170</t>
+          <t>1351706</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1417185</t>
+          <t>1397360</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>93,67%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>25955</t>
+          <t>29562</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10361</t>
+          <t>19238</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>41222</t>
+          <t>43749</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>28612</t>
+          <t>33823</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>21205</t>
+          <t>24481</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>39507</t>
+          <t>46689</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>54567</t>
+          <t>63385</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>32849</t>
+          <t>49499</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>72603</t>
+          <t>81045</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>902765</t>
+          <t>768510</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>887498</t>
+          <t>754323</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>918359</t>
+          <t>778834</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>689119</t>
+          <t>797508</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>678224</t>
+          <t>784642</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>696526</t>
+          <t>806850</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1591885</t>
+          <t>1566018</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1573849</t>
+          <t>1548358</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1613603</t>
+          <t>1579904</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>96,96%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>200059</t>
+          <t>221023</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>153650</t>
+          <t>190405</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>236555</t>
+          <t>255818</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>213603</t>
+          <t>232180</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>172841</t>
+          <t>207634</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>242043</t>
+          <t>261005</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>413662</t>
+          <t>453203</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>352614</t>
+          <t>414681</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>461129</t>
+          <t>500325</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3259758</t>
+          <t>3311739</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3223262</t>
+          <t>3276944</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3306167</t>
+          <t>3342357</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3448554</t>
+          <t>3503071</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3420114</t>
+          <t>3474246</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3489316</t>
+          <t>3527617</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6708312</t>
+          <t>6814810</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6660845</t>
+          <t>6767688</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6769360</t>
+          <t>6853332</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,29%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3662157</t>
+          <t>3735251</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3662157</t>
+          <t>3735251</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3662157</t>
+          <t>3735251</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7121974</t>
+          <t>7268013</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7121974</t>
+          <t>7268013</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7121974</t>
+          <t>7268013</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
